--- a/DEV/org.openl.rules.test/test-resources/functionality/EPBDS-13198_strictLess_and_strictGreater_comparisonOpsDouble.xlsx
+++ b/DEV/org.openl.rules.test/test-resources/functionality/EPBDS-13198_strictLess_and_strictGreater_comparisonOpsDouble.xlsx
@@ -2,16 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
+  <bookViews>
+    <workbookView activeTab="0"/>
+  </bookViews>
   <sheets>
     <sheet state="visible" name="DoubleComparison" sheetId="1" r:id="rId4"/>
   </sheets>
-  <definedNames/>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="147">
   <si>
     <t>// There are some problems with Double rounding in OpenL; The next tests will be compared result for different double types: 'd, Double, double'</t>
   </si>
@@ -322,12 +324,151 @@
   </si>
   <si>
     <t>Test GreaterThanAndGreaterThanOrEqDivision</t>
+  </si>
+  <si>
+    <t>// Double arithmetic computes with the decimals the numbers show, but a quotient without a finite decimal is rounded to a Double. The next tests will be compared result for different double types: 'd, Double, double'</t>
+  </si>
+  <si>
+    <t>// In the DoubleAddition case in OpenL result will be ( 0.9999999999999999 ) instead 1</t>
+  </si>
+  <si>
+    <t>// The tests below will be checked the comparing  between ( 0.9999999999999999 ) and ( 1 )</t>
+  </si>
+  <si>
+    <t>// In the DoubleSubtraction case in OpenL result will be ( 0.7933333333333334 ) instead 0.7933333333333333</t>
+  </si>
+  <si>
+    <t>// The tests below will be checked the comparing  between ( 0.7933333333333334 ) and ( 0.7933333333333333 )</t>
+  </si>
+  <si>
+    <t>// In the DoubleMultiplication case in OpenL result will be ( 0.9999999999999999 ) instead 1</t>
+  </si>
+  <si>
+    <t>// In the DoubleDivision case in OpenL result will be ( 3.0000000000000004 ) instead 3</t>
+  </si>
+  <si>
+    <t>// The tests below will be checked the comparing  between ( 3.0000000000000004 ) and ( 3 )</t>
+  </si>
+  <si>
+    <t>= 1d / 3d + 2d / 3d</t>
+  </si>
+  <si>
+    <t>= (Double) 1 / (Double) 3 + (Double) 2 / (Double) 3</t>
+  </si>
+  <si>
+    <t>= (double) 1 / (double) 3 + (double) 2 / (double) 3</t>
+  </si>
+  <si>
+    <t>= 1d</t>
+  </si>
+  <si>
+    <t>= (Double) 1</t>
+  </si>
+  <si>
+    <t>= (double) 1</t>
+  </si>
+  <si>
+    <t>= 5d / 6d - 0.04d</t>
+  </si>
+  <si>
+    <t>= (Double) 5 / (Double) 6 - (Double) 0.04</t>
+  </si>
+  <si>
+    <t>= (double) 5 / (double) 6 - (double) 0.04</t>
+  </si>
+  <si>
+    <t>= 0.7933333333333333d</t>
+  </si>
+  <si>
+    <t>= (Double) 0.7933333333333333</t>
+  </si>
+  <si>
+    <t>= (double) 0.7933333333333333</t>
+  </si>
+  <si>
+    <t>= 1d / 3d * 3d</t>
+  </si>
+  <si>
+    <t>= (Double) 1 / (Double) 3 * (Double) 3</t>
+  </si>
+  <si>
+    <t>= (double) 1 / (double) 3 * (double) 3</t>
+  </si>
+  <si>
+    <t>= 1d / (1d / 3d)</t>
+  </si>
+  <si>
+    <t>= (Double) 1 / ((Double) 1 / (Double) 3)</t>
+  </si>
+  <si>
+    <t>= (double) 1 / ((double) 1 / (double) 3)</t>
+  </si>
+  <si>
+    <t>= 3d</t>
+  </si>
+  <si>
+    <t>= (Double) 3</t>
+  </si>
+  <si>
+    <t>= (double) 3</t>
+  </si>
+  <si>
+    <t>= 1.0000000000000002d</t>
+  </si>
+  <si>
+    <t>= (Double) 1.0000000000000002</t>
+  </si>
+  <si>
+    <t>= (double) 1.0000000000000002</t>
+  </si>
+  <si>
+    <t>= 0.7933333333333332d</t>
+  </si>
+  <si>
+    <t>= (Double) 0.7933333333333332</t>
+  </si>
+  <si>
+    <t>= (double) 0.7933333333333332</t>
+  </si>
+  <si>
+    <t>= 2.9999999999999996d</t>
+  </si>
+  <si>
+    <t>= (Double) 2.9999999999999996</t>
+  </si>
+  <si>
+    <t>= (double) 2.9999999999999996</t>
+  </si>
+  <si>
+    <t>// Double arithmetic computes with the decimals the numbers show, and a computed number of 16 or 17 digits, such as a quotient, counts as its Double. The next tests will be compared result for different double types: 'd, Double, double'</t>
+  </si>
+  <si>
+    <t>// In the DoubleAddition case in OpenL result will be ( 1 ): 1/3 and 2/3 count as their Doubles, whose sum rounds to 1</t>
+  </si>
+  <si>
+    <t>// The tests below will be checked the comparing  between ( 1 ) and the next Double ( 1.0000000000000002 )</t>
+  </si>
+  <si>
+    <t>// In the DoubleSubtraction case in OpenL result will be ( 0.7933333333333333 ): 5/6 counts as its Double and 0.04 as the decimal it shows</t>
+  </si>
+  <si>
+    <t>// The tests below will be checked the comparing  between ( 0.7933333333333333 ) and the previous Double ( 0.7933333333333332 )</t>
+  </si>
+  <si>
+    <t>// In the DoubleMultiplication case in OpenL result will be ( 1 ): 1/3 counts as its Double</t>
+  </si>
+  <si>
+    <t>// In the DoubleDivision case in OpenL result will be ( 3 ): 1/3 counts as its Double</t>
+  </si>
+  <si>
+    <t>// The tests below will be checked the comparing  between ( 3 ) and the previous Double ( 2.9999999999999996 )</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <numFmts count="0"/>
   <fonts count="9">
     <font>
       <sz val="10.0"/>
@@ -756,25 +897,26 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
+  <dimension ref="A2:Z150"/>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="3" max="3" width="27.0"/>
-    <col customWidth="1" min="4" max="4" width="30.25"/>
-    <col customWidth="1" min="5" max="5" width="31.0"/>
-    <col customWidth="1" min="6" max="6" width="24.5"/>
-    <col customWidth="1" min="7" max="7" width="34.13"/>
-    <col customWidth="1" min="8" max="8" width="34.38"/>
-    <col customWidth="1" min="9" max="9" width="33.38"/>
-    <col customWidth="1" min="10" max="10" width="33.0"/>
-    <col customWidth="1" min="11" max="11" width="32.5"/>
-    <col customWidth="1" min="12" max="12" width="32.63"/>
-    <col customWidth="1" min="13" max="13" width="33.25"/>
-    <col customWidth="1" min="14" max="14" width="33.63"/>
+    <col min="3" max="3" customWidth="true" width="27.0"/>
+    <col min="4" max="4" customWidth="true" width="30.25"/>
+    <col min="5" max="5" customWidth="true" width="31.0"/>
+    <col min="6" max="6" customWidth="true" width="24.5"/>
+    <col min="7" max="7" customWidth="true" width="34.13"/>
+    <col min="8" max="8" customWidth="true" width="34.38"/>
+    <col min="9" max="9" customWidth="true" width="33.38"/>
+    <col min="10" max="10" customWidth="true" width="33.0"/>
+    <col min="11" max="11" customWidth="true" width="32.5"/>
+    <col min="12" max="12" customWidth="true" width="32.63"/>
+    <col min="13" max="13" customWidth="true" width="33.25"/>
+    <col min="14" max="14" customWidth="true" width="33.63"/>
   </cols>
   <sheetData>
     <row r="2">
       <c r="B2" s="1" t="s">
-        <v>0</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4">
@@ -784,12 +926,12 @@
     </row>
     <row r="5">
       <c r="B5" s="2" t="s">
-        <v>2</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="2" t="s">
-        <v>3</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8">
@@ -819,13 +961,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>10</v>
+        <v>109</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>12</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11">
@@ -833,13 +975,13 @@
         <v>13</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>14</v>
+        <v>130</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>15</v>
+        <v>131</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>16</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12">
@@ -1075,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>10</v>
+        <v>109</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>12</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29">
@@ -1089,13 +1231,13 @@
         <v>13</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>14</v>
+        <v>130</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>15</v>
+        <v>131</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>16</v>
+        <v>132</v>
       </c>
     </row>
     <row r="30">
@@ -1311,12 +1453,12 @@
     </row>
     <row r="43">
       <c r="B43" s="2" t="s">
-        <v>63</v>
+        <v>142</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="2" t="s">
-        <v>64</v>
+        <v>143</v>
       </c>
     </row>
     <row r="46">
@@ -1346,13 +1488,13 @@
         <v>9</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>66</v>
+        <v>115</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>67</v>
+        <v>116</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>68</v>
+        <v>117</v>
       </c>
     </row>
     <row r="49">
@@ -1360,13 +1502,13 @@
         <v>13</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>69</v>
+        <v>133</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>70</v>
+        <v>134</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>71</v>
+        <v>135</v>
       </c>
     </row>
     <row r="50">
@@ -1647,13 +1789,13 @@
         <v>9</v>
       </c>
       <c r="C65" s="18" t="s">
-        <v>66</v>
+        <v>115</v>
       </c>
       <c r="D65" s="18" t="s">
-        <v>67</v>
+        <v>116</v>
       </c>
       <c r="E65" s="18" t="s">
-        <v>68</v>
+        <v>117</v>
       </c>
       <c r="F65" s="15"/>
       <c r="G65" s="15"/>
@@ -1683,13 +1825,13 @@
         <v>13</v>
       </c>
       <c r="C66" s="19" t="s">
-        <v>69</v>
+        <v>133</v>
       </c>
       <c r="D66" s="19" t="s">
-        <v>70</v>
+        <v>134</v>
       </c>
       <c r="E66" s="19" t="s">
-        <v>71</v>
+        <v>135</v>
       </c>
       <c r="F66" s="15"/>
       <c r="G66" s="15"/>
@@ -2062,12 +2204,12 @@
     </row>
     <row r="80">
       <c r="B80" s="2" t="s">
-        <v>76</v>
+        <v>144</v>
       </c>
     </row>
     <row r="81">
       <c r="B81" s="2" t="s">
-        <v>77</v>
+        <v>141</v>
       </c>
     </row>
     <row r="83">
@@ -2142,13 +2284,13 @@
         <v>9</v>
       </c>
       <c r="C85" s="18" t="s">
-        <v>79</v>
+        <v>121</v>
       </c>
       <c r="D85" s="18" t="s">
-        <v>80</v>
+        <v>122</v>
       </c>
       <c r="E85" s="18" t="s">
-        <v>81</v>
+        <v>123</v>
       </c>
       <c r="F85" s="15"/>
       <c r="G85" s="15"/>
@@ -2178,13 +2320,13 @@
         <v>13</v>
       </c>
       <c r="C86" s="18" t="s">
-        <v>82</v>
+        <v>130</v>
       </c>
       <c r="D86" s="18" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="E86" s="18" t="s">
-        <v>84</v>
+        <v>132</v>
       </c>
       <c r="F86" s="15"/>
       <c r="G86" s="15"/>
@@ -2622,13 +2764,13 @@
         <v>9</v>
       </c>
       <c r="C102" s="18" t="s">
-        <v>79</v>
+        <v>121</v>
       </c>
       <c r="D102" s="18" t="s">
-        <v>80</v>
+        <v>122</v>
       </c>
       <c r="E102" s="18" t="s">
-        <v>81</v>
+        <v>123</v>
       </c>
       <c r="F102" s="15"/>
       <c r="G102" s="15"/>
@@ -2658,13 +2800,13 @@
         <v>13</v>
       </c>
       <c r="C103" s="18" t="s">
-        <v>82</v>
+        <v>130</v>
       </c>
       <c r="D103" s="18" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="E103" s="18" t="s">
-        <v>84</v>
+        <v>132</v>
       </c>
       <c r="F103" s="15"/>
       <c r="G103" s="15"/>
@@ -3037,12 +3179,12 @@
     </row>
     <row r="117">
       <c r="B117" s="2" t="s">
-        <v>89</v>
+        <v>145</v>
       </c>
     </row>
     <row r="118">
       <c r="B118" s="2" t="s">
-        <v>90</v>
+        <v>146</v>
       </c>
     </row>
     <row r="120">
@@ -3117,13 +3259,13 @@
         <v>9</v>
       </c>
       <c r="C122" s="18" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="D122" s="18" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="E122" s="18" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="F122" s="15"/>
       <c r="G122" s="15"/>
@@ -3153,13 +3295,13 @@
         <v>13</v>
       </c>
       <c r="C123" s="18" t="s">
-        <v>95</v>
+        <v>136</v>
       </c>
       <c r="D123" s="18" t="s">
-        <v>96</v>
+        <v>137</v>
       </c>
       <c r="E123" s="18" t="s">
-        <v>97</v>
+        <v>138</v>
       </c>
       <c r="F123" s="15"/>
       <c r="G123" s="15"/>
@@ -3597,13 +3739,13 @@
         <v>9</v>
       </c>
       <c r="C139" s="18" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="D139" s="18" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="E139" s="18" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="F139" s="15"/>
       <c r="G139" s="15"/>
@@ -3633,13 +3775,13 @@
         <v>13</v>
       </c>
       <c r="C140" s="18" t="s">
-        <v>95</v>
+        <v>136</v>
       </c>
       <c r="D140" s="18" t="s">
-        <v>96</v>
+        <v>137</v>
       </c>
       <c r="E140" s="18" t="s">
-        <v>97</v>
+        <v>138</v>
       </c>
       <c r="F140" s="15"/>
       <c r="G140" s="15"/>
